--- a/ig/main/CodeSystem-TRE-R31-StatutEtatCivil.xlsx
+++ b/ig/main/CodeSystem-TRE-R31-StatutEtatCivil.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>urn:ietf:rfc:3986#Uniform Resource Identifier (URI)#urn:oid:1.2.250.1.213.1.6.1.9</t>
+    <t>OID:1.2.250.1.213.1.6.1.9</t>
   </si>
   <si>
     <t>Version</t>

--- a/ig/main/CodeSystem-TRE-R31-StatutEtatCivil.xlsx
+++ b/ig/main/CodeSystem-TRE-R31-StatutEtatCivil.xlsx
@@ -76,7 +76,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ig/main/CodeSystem-TRE-R31-StatutEtatCivil.xlsx
+++ b/ig/main/CodeSystem-TRE-R31-StatutEtatCivil.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="65">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2024-03-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -194,6 +194,9 @@
   </si>
   <si>
     <t>Certifié par FranceConnect</t>
+  </si>
+  <si>
+    <t>FranceConnect est un dispositif qui permet aux internautes de s'identifier sur un service en ligne par l'intermédiaire d'un compte existant (impots.gouv.fr, ameli.fr…). Les données d'état civil récupérées depuis le Répertoire national d'identification des personnes physiques de l'Insee (RNIPP) lors de l'identification par FranceConnect sont certifiées par l'Insee.</t>
   </si>
   <si>
     <t>NC</t>
@@ -654,17 +657,19 @@
       <c r="C6" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -673,10 +678,10 @@
         <v>49</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" s="2"/>
     </row>

--- a/ig/main/CodeSystem-TRE-R31-StatutEtatCivil.xlsx
+++ b/ig/main/CodeSystem-TRE-R31-StatutEtatCivil.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>20240329120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/CodeSystem-TRE-R31-StatutEtatCivil.xlsx
+++ b/ig/main/CodeSystem-TRE-R31-StatutEtatCivil.xlsx
@@ -82,7 +82,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
